--- a/ksoft/docs/records/Sales_Repres_Records.xlsx
+++ b/ksoft/docs/records/Sales_Repres_Records.xlsx
@@ -1595,13 +1595,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A42B113-8850-4550-BD93-C7A750E052BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532C2CD1-DEF6-4F55-8FC0-0511E29AAAFE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49883D06-FEDD-4560-A645-7966232D9B88}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E072178D-F8AE-4B7B-AB19-E430E6F860E1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF16CC4-F305-49DF-9D7B-A88BF484E0B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86D8062-F31B-4E20-A1B8-BEF59AB8527E}"/>
 </file>
--- a/ksoft/docs/records/Sales_Repres_Records.xlsx
+++ b/ksoft/docs/records/Sales_Repres_Records.xlsx
@@ -1595,13 +1595,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{532C2CD1-DEF6-4F55-8FC0-0511E29AAAFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A42B113-8850-4550-BD93-C7A750E052BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E072178D-F8AE-4B7B-AB19-E430E6F860E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49883D06-FEDD-4560-A645-7966232D9B88}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C86D8062-F31B-4E20-A1B8-BEF59AB8527E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CF16CC4-F305-49DF-9D7B-A88BF484E0B5}"/>
 </file>